--- a/docs/데이터_출처표.xlsx
+++ b/docs/데이터_출처표.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="174">
   <si>
     <r>
       <rPr>
@@ -714,7 +714,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">유해화학물질 저장 관련 지침</t>
+      <t xml:space="preserve">유해화학물질 저장 운반 및 취급에 관한 기술지침</t>
     </r>
   </si>
   <si>
@@ -733,7 +733,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">유해화학물질 저장…지침</t>
+      <t xml:space="preserve">유해화학물질 저장 운반 및 취급에 관한 기술지침</t>
     </r>
     <r>
       <rPr>
@@ -758,16 +758,1416 @@
     <t xml:space="preserve">https://www.kosha.or.kr</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">문서명 일부는 파일명 기준</t>
-    </r>
-    <r>
-      <rPr>
+    <t xml:space="preserve">K2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">G-9-2013 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">위험물질 취급작업장 위험표시에 관한 기술지침</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">G-9-2013_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">위험물질</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">취급작업장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">위험표시에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">관한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기술지침</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-11</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">위험표시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">경고표지 내용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, 11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">청크</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">K3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">G-12-2013 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개인보호구의 사용 및 관리에 관한 기술지침</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">G-12-2013_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개인보호구의…술지침</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공표일 기준</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K4</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">W-14-2020 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">경고표지 작성 지침</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">W-14-2020 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">경고표지 작성 지침</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K5</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">W-15-2020 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">물질안전보건자료 작성 지침</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">W-15-2020 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">물질안전보건자료…지침</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">K6</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">W-16-2020 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">화학물질의 유해성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">위험성 분류 지침</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">W-16-2020 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">화학물질의 유해…지침</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.pdf</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">130</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">청크로 큰 편</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">K7</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">X-27-2012 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">화학물질 리스크 관리를 위한 작업공정별 관리요령에 관한 지침</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">X-27-2012_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">화학물질 리스크…지침</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K8</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H-123-2013 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">불산</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">불화수소 취급근로자의 중독 예방 및 응급대응 지침</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H-123-2013 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">불산</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">불화수소…지침</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-12</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">불산 응급대응 근거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, 26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">청크</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">D1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSDS</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">황산 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MSDS (Sulfuric acid, Sigma-Aldrich Korea)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Sigma-Aldrich_MSDS.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sigma-Aldrich Korea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 항목 전체</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">sigma-339741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7664-93-9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.sigmaaldrich.com/KR/ko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">불산 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MSDS (Hydrofluoric acid, Sigma-Aldrich Korea)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">불산</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">한국어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sigma-695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7664-39-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">과산화수소 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MSDS (Hydrogen peroxide 30%, Merck(Millipore))</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">과산화수소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">한국어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Merck(Millipore)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">merck-8.22287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7722-84-1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공급자 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Merck</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">D4</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">암모니아수 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MSDS (Ammonium hydroxide solution, Sigma-Aldrich Korea)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">암모니아수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">한국어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sigma-221228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1336-21-6</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">항목 줄이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개로 잡힘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">적재 시 확인</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">D5</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">염산 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MSDS (Hydrochloric acid, Sigma-Aldrich Korea)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">염산</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">한국어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sigma-258148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7647-01-0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D6</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">질산 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MSDS (Nitric acid, Sigma-Aldrich Korea)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">질산</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">한국어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sigma-438073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7697-37-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D7</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인산 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MSDS (ortho-Phosphoric acid 85%, Merck(Millipore))</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인산</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">merck-1.00573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7664-38-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMAH MSDS (Tetramethylammonium hydroxide solution, Sigma-Aldrich Korea)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMAH.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sigma-328251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75-59-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D9</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아세톤 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MSDS (Acetone, Sigma-Aldrich Korea)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아세톤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">sigma-179124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67-64-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D10</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">메탄올 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MSDS (Methanol, Sigma-Aldrich Korea)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">메탄올</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sigma-34860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67-56-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공급자 확인 필요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D11</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IPA(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이소프로판올</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) MSDS (Isopropanol, Sigma-Aldrich Korea)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">IPA.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sigma-563935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67-63-0</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">함유량 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">70~75%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 희석 제품</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">D12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGMEA MSDS (Propylene glycol monomethyl ether acetate, Sigma-Aldrich Korea)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGMEA.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sigma-484431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108-65-6</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">함유량 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">95% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이상</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">D13</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수산화나트륨 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MSDS (Sodium hydroxide, Sigma-Aldrich Korea)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수산화나트륨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">sigma-221465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1310-73-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">데이터 출처 요약</t>
+  </si>
+  <si>
+    <t xml:space="preserve">파일 수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적재 완료</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적재 완료 비율</t>
+  </si>
+  <si>
+    <t xml:space="preserve">합계</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">교재 기준</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: 5~30</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
@@ -777,14 +2177,35 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확인 필요</t>
-    </r>
-    <r>
-      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">현재 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">26</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
@@ -794,1366 +2215,124 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">K2</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">G-9-2013 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">위험물 취급장소 관련 지침</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">G-9-2013_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">위험물</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">취급…술지침</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.pdf</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2013-11</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">경고표지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안전보건표지 내용</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, 11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">청크</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">K3</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">G-12-2013 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개인보호구의 사용 및 관리에 관한 기술지침</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">G-12-2013_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개인보호구의…술지침</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.pdf</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2013-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공표일 기준</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K4</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">W-14-2020 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">경고표지 작성 지침</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">W-14-2020 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">경고표지 작성 지침</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.pdf</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K5</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">W-15-2020 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">물질안전보건자료 작성 지침</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">W-15-2020 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">물질안전보건자료…지침</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.pdf</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">K6</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">W-16-2020 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">화학물질의 유해성</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">위험성 분류 지침</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">W-16-2020 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">화학물질의 유해…지침</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.pdf</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">130</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">청크로 큰 편</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">K7</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">X-27-2012 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">화학물질 리스크 관리를 위한 작업공정별 관리요령에 관한 지침</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">X-27-2012_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">화학물질 리스크…지침</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.pdf</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2012-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K8</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">H-123-2013 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">불산</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">불화수소 취급근로자의 중독 예방 및 응급대응 지침</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">H-123-2013 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">불산</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">불화수소…지침</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.pdf</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2013-12</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">불산 응급대응 근거</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, 26</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">청크</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">D1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSDS</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">황산 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MSDS (Sulfuric acid, Sigma-Aldrich Korea)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Sigma-Aldrich_MSDS.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sigma-Aldrich Korea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개 항목 전체</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">sigma-339741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7664-93-9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.sigmaaldrich.com/KR/ko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D2</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">불산 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MSDS (Hydrofluoric acid, Sigma-Aldrich Korea)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">불산</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">한국어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.pdf</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sigma-695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7664-39-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D3</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">과산화수소 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MSDS (Hydrogen peroxide 30%, Merck(Millipore))</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">과산화수소</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">한국어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.pdf</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Merck(Millipore)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">merck-8.22287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7722-84-1</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">공급자 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Merck</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">D4</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">암모니아수 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MSDS (Ammonium hydroxide solution, Sigma-Aldrich Korea)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">암모니아수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">한국어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.pdf</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sigma-221228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1336-21-6</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">항목 줄이 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개로 잡힘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">적재 시 확인</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">D5</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">염산 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MSDS (Hydrochloric acid, Sigma-Aldrich Korea)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">염산</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">한국어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.pdf</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sigma-258148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7647-01-0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D6</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">질산 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MSDS (Nitric acid, Sigma-Aldrich Korea)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">질산</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">한국어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.pdf</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sigma-438073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7697-37-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D7</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">인산 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MSDS (ortho-Phosphoric acid 85%, Merck(Millipore))</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">인산</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.pdf</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">merck-1.00573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7664-38-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMAH MSDS (Tetramethylammonium hydroxide solution, Sigma-Aldrich Korea)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMAH.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sigma-328251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75-59-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D9</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">아세톤 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MSDS (Acetone, Sigma-Aldrich Korea)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">아세톤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.pdf</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">sigma-179124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67-64-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D10</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">메탄올 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MSDS (Methanol, Sigma-Aldrich Korea)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">메탄올</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.pdf</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sigma-34860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67-56-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공급자 확인 필요</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D11</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">IPA(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이소프로판올</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) MSDS (Isopropanol, Sigma-Aldrich Korea)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">IPA.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sigma-563935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67-63-0</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">함유량 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">70~75%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">의 희석 제품</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">D12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGMEA MSDS (Propylene glycol monomethyl ether acetate, Sigma-Aldrich Korea)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGMEA.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sigma-484431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108-65-6</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">함유량 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">95% </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이상</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">D13</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">수산화나트륨 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MSDS (Sodium hydroxide, Sigma-Aldrich Korea)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">수산화나트륨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.pdf</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">sigma-221465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1310-73-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">데이터 출처 요약</t>
-  </si>
-  <si>
-    <t xml:space="preserve">파일 수</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적재 완료</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적재 완료 비율</t>
-  </si>
-  <si>
-    <t xml:space="preserve">합계</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">교재 기준</t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: 5~30</t>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">출처표</t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개 </t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">적재 상태</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">' </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">열을 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">적재 완료</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 바꾸면 이 표가 자동으로 갱신돼요 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -2167,7 +2346,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">현재 </t>
+      <t xml:space="preserve">파란 글씨 </t>
     </r>
     <r>
       <rPr>
@@ -2177,7 +2356,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">26</t>
+      <t xml:space="preserve">= </t>
     </r>
     <r>
       <rPr>
@@ -2186,7 +2365,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">개</t>
+      <t xml:space="preserve">직접 수정하는 칸</t>
     </r>
     <r>
       <rPr>
@@ -2196,193 +2375,10 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">출처표</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">의 </t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">적재 상태</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">' </t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">열을 </t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">적재 완료</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로 바꾸면 이 표가 자동으로 갱신돼요 </t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">파란 글씨 </t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">= </t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">직접 수정하는 칸</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
       <t xml:space="preserve">).</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일부 문서명은 파일명 기준이고</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
     <r>
       <rPr>
         <i val="true"/>
@@ -3273,7 +3269,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
         <v>44</v>
       </c>
@@ -3306,28 +3302,26 @@
       <c r="L7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M7" s="5" t="s">
+      <c r="M7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
-        <v>53</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>45</v>
       </c>
       <c r="C8" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>48</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>37</v>
@@ -3344,27 +3338,27 @@
         <v>22</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>45</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>60</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>48</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>37</v>
@@ -3381,27 +3375,27 @@
         <v>22</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>45</v>
       </c>
       <c r="C10" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>65</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>48</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>37</v>
@@ -3421,22 +3415,22 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>45</v>
       </c>
       <c r="C11" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>68</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>69</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>48</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>37</v>
@@ -3456,22 +3450,22 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>45</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>71</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>72</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>48</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>37</v>
@@ -3488,27 +3482,27 @@
         <v>22</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>45</v>
       </c>
       <c r="C13" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>48</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>37</v>
@@ -3528,22 +3522,22 @@
     </row>
     <row r="14" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>45</v>
       </c>
       <c r="C14" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>48</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>37</v>
@@ -3560,42 +3554,42 @@
         <v>22</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="C15" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="E15" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="F15" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="G15" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>89</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>50</v>
       </c>
       <c r="I15" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J15" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="J15" s="6" t="s">
+      <c r="K15" s="7" t="s">
         <v>91</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>92</v>
       </c>
       <c r="L15" s="8" t="s">
         <v>22</v>
@@ -3604,37 +3598,37 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C16" s="5" t="s">
+      <c r="D16" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F16" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>96</v>
-      </c>
       <c r="G16" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>50</v>
       </c>
       <c r="I16" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="J16" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="J16" s="6" t="s">
-        <v>98</v>
-      </c>
       <c r="K16" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L16" s="8" t="s">
         <v>22</v>
@@ -3643,119 +3637,119 @@
     </row>
     <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="F17" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="F17" s="6" t="s">
-        <v>103</v>
-      </c>
       <c r="G17" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>50</v>
       </c>
       <c r="I17" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="J17" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="J17" s="6" t="s">
-        <v>105</v>
-      </c>
       <c r="K17" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L17" s="8" t="s">
         <v>22</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" s="5" t="s">
+      <c r="D18" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="E18" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F18" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>110</v>
-      </c>
       <c r="G18" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>50</v>
       </c>
       <c r="I18" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="J18" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="J18" s="6" t="s">
-        <v>112</v>
-      </c>
       <c r="K18" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L18" s="8" t="s">
         <v>22</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C19" s="5" t="s">
+      <c r="D19" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="E19" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F19" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E19" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>117</v>
-      </c>
       <c r="G19" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>50</v>
       </c>
       <c r="I19" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="J19" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="J19" s="6" t="s">
-        <v>119</v>
-      </c>
       <c r="K19" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L19" s="8" t="s">
         <v>22</v>
@@ -3764,37 +3758,37 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="E20" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F20" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>123</v>
-      </c>
       <c r="G20" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>50</v>
       </c>
       <c r="I20" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="J20" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="J20" s="6" t="s">
-        <v>125</v>
-      </c>
       <c r="K20" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L20" s="8" t="s">
         <v>22</v>
@@ -3803,78 +3797,78 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F21" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>129</v>
-      </c>
       <c r="G21" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>50</v>
       </c>
       <c r="I21" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="J21" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="J21" s="6" t="s">
-        <v>131</v>
-      </c>
       <c r="K21" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L21" s="8" t="s">
         <v>22</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="B22" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" s="6" t="s">
+      <c r="D22" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>134</v>
-      </c>
       <c r="E22" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F22" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="G22" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>89</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>50</v>
       </c>
       <c r="I22" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="J22" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="J22" s="6" t="s">
-        <v>136</v>
-      </c>
       <c r="K22" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L22" s="8" t="s">
         <v>22</v>
@@ -3883,37 +3877,37 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="B23" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23" s="5" t="s">
+      <c r="D23" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>139</v>
-      </c>
       <c r="E23" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F23" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="G23" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>89</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>50</v>
       </c>
       <c r="I23" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="J23" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="J23" s="6" t="s">
-        <v>141</v>
-      </c>
       <c r="K23" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L23" s="8" t="s">
         <v>22</v>
@@ -3922,160 +3916,160 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="B24" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C24" s="5" t="s">
+      <c r="D24" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="E24" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F24" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="E24" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>145</v>
-      </c>
       <c r="G24" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>50</v>
       </c>
       <c r="I24" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="J24" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J24" s="6" t="s">
-        <v>147</v>
-      </c>
       <c r="K24" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L24" s="8" t="s">
         <v>22</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="B25" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C25" s="6" t="s">
+      <c r="D25" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="E25" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F25" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="E25" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>152</v>
-      </c>
       <c r="G25" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>50</v>
       </c>
       <c r="I25" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="J25" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="J25" s="6" t="s">
-        <v>154</v>
-      </c>
       <c r="K25" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L25" s="8" t="s">
         <v>22</v>
       </c>
       <c r="M25" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="B26" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C26" s="6" t="s">
+      <c r="D26" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>158</v>
-      </c>
       <c r="E26" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F26" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="G26" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>89</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>50</v>
       </c>
       <c r="I26" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="J26" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="J26" s="6" t="s">
-        <v>160</v>
-      </c>
       <c r="K26" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L26" s="8" t="s">
         <v>22</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="B27" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C27" s="5" t="s">
+      <c r="D27" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>164</v>
-      </c>
       <c r="E27" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>50</v>
       </c>
       <c r="I27" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="J27" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="J27" s="6" t="s">
-        <v>166</v>
-      </c>
       <c r="K27" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L27" s="8" t="s">
         <v>22</v>
@@ -4137,7 +4131,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4145,13 +4139,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="D3" s="12" t="s">
         <v>169</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4190,7 +4184,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B6" s="15" t="n">
         <f aca="false">COUNTIF(출처표!$B$2:$B$27,A6)</f>
@@ -4207,7 +4201,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B7" s="16" t="n">
         <f aca="false">SUM(B4:B6)</f>
@@ -4224,17 +4218,17 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/docs/데이터_출처표.xlsx
+++ b/docs/데이터_출처표.xlsx
@@ -211,7 +211,125 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">산업안전보건법</t>
+      <t xml:space="preserve">산안법</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">국가법령정보센터</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110-116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">faiss_db/law</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.law.go.kr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적재 전</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MSDS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">관련 제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">110~116</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">산업안전보건기준에 관한 규칙</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안전보건규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31-34,299,420-511</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">515</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조</t>
     </r>
     <r>
       <rPr>
@@ -228,33 +346,68 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">법률</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">제</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">21374</t>
+      <t xml:space="preserve">난청</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 범위 밖</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">산업안전보건법 시행규칙</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시행규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">156-171</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고용노동부령 제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">477</t>
     </r>
     <r>
       <rPr>
@@ -271,211 +424,82 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)(20260801).pdf</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">국가법령정보센터</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110-116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">faiss_db/law</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.law.go.kr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적재 전</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MSDS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">관련 제</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">110~116</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">조</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">산업안전보건기준에 관한 규칙</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">산업안전보건기준에 관한 규칙…</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">302).pdf</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31-34,299,420-511</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">제</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">515</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">조</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">난청</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">는 범위 밖</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">산업안전보건법 시행규칙</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">산업안전보건법 시행규칙</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">고용…</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">801).pdf</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">156-171</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">고용노동부령 제</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">477</t>
+      <t xml:space="preserve">, MSDS·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">경고표시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">교육</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">L2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">중대재해 처벌 등에 관한 법률</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중대재해처벌법</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-01-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전체</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">법률 제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17907</t>
     </r>
     <r>
       <rPr>
@@ -492,15 +516,206 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">, MSDS·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">경고표시</t>
+      <t xml:space="preserve">, 16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">청크</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">L3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화학물질관리법</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">화관법</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-08</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원문 시행 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-08</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">K1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">KOSHA </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지침</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">K-1-2023 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">유해화학물질 저장 운반 및 취급에 관한 기술지침</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">K-1_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">화학물질저장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">한국산업안전보건공단</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">faiss_db/msds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.kosha.or.kr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">G-9-2013 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">위험물질 취급작업장 위험표시에 관한 기술지침</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">G-9_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">위험표시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-11</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">위험표시</t>
     </r>
     <r>
       <rPr>
@@ -517,74 +732,16 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">교육</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">L2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">중대재해 처벌 등에 관한 법률</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">중대재해 처벌 등에 관한 법률…</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">127).pdf</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-01-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전체</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">법률 제</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">17907</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">호</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, 16</t>
+      <t xml:space="preserve">경고표지 내용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, 11</t>
     </r>
     <r>
       <rPr>
@@ -596,144 +753,44 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">L3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화학물질관리법</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">화학물질관리법</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">법률</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">제</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2153…008).pdf</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-08</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원문 시행 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-10-08</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">K1</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">KOSHA </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지침</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">K-1-2023 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">유해화학물질 저장 운반 및 취급에 관한 기술지침</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">K-1-2023 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">유해화학물질 저장 운반 및 취급에 관한 기술지침</t>
+    <t xml:space="preserve">K3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">G-12-2013 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개인보호구의 사용 및 관리에 관한 기술지침</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">G-12_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개인보호구</t>
     </r>
     <r>
       <rPr>
@@ -746,124 +803,50 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">한국산업안전보건공단</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">faiss_db/msds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.kosha.or.kr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K2</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">G-9-2013 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">위험물질 취급작업장 위험표시에 관한 기술지침</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">G-9-2013_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">위험물질</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">취급작업장</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">위험표시에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">관한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기술지침</t>
+    <t xml:space="preserve">2013-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공표일 기준</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K4</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">W-14-2020 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">경고표지 작성 지침</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">W-14_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">경고표지</t>
     </r>
     <r>
       <rPr>
@@ -876,16 +859,78 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">2013-11</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">위험표시</t>
+    <t xml:space="preserve">2020-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K5</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">W-15-2020 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">물질안전보건자료 작성 지침</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">W-15_MSDS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">작성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">K6</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">W-16-2020 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">화학물질의 유해성</t>
     </r>
     <r>
       <rPr>
@@ -902,16 +947,196 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">경고표지 내용</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, 11</t>
+      <t xml:space="preserve">위험성 분류 지침</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">W-16_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">유해성분류</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.pdf</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">130</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">청크로 큰 편</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">K7</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">X-27-2012 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">화학물질 리스크 관리를 위한 작업공정별 관리요령에 관한 지침</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">X-27_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">리스크관리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K8</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H-123-2013 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">불산</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">불화수소 취급근로자의 중독 예방 및 응급대응 지침</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H-123_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">불산지침</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-12</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">불산 응급대응 근거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, 26</t>
     </r>
     <r>
       <rPr>
@@ -923,44 +1148,38 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">K3</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">G-12-2013 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개인보호구의 사용 및 관리에 관한 기술지침</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">G-12-2013_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개인보호구의…술지침</t>
+    <t xml:space="preserve">D1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSDS</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">황산 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MSDS (Sulfuric acid, Sigma-Aldrich Korea)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">황산</t>
     </r>
     <r>
       <rPr>
@@ -973,50 +1192,69 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">2013-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공표일 기준</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K4</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">W-14-2020 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">경고표지 작성 지침</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">W-14-2020 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">경고표지 작성 지침</t>
+    <t xml:space="preserve">Sigma-Aldrich Korea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 항목 전체</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">sigma-339741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7664-93-9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.sigmaaldrich.com/KR/ko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">불산 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MSDS (Hydrofluoric acid, Sigma-Aldrich Korea)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">불산</t>
     </r>
     <r>
       <rPr>
@@ -1029,47 +1267,44 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">2020-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K5</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">W-15-2020 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">물질안전보건자료 작성 지침</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">W-15-2020 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">물질안전보건자료…지침</t>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sigma-695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7664-39-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">과산화수소 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MSDS (Hydrogen peroxide 30%, Merck(Millipore))</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">과산화수소</t>
     </r>
     <r>
       <rPr>
@@ -1082,61 +1317,66 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">K6</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">W-16-2020 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">화학물질의 유해성</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">위험성 분류 지침</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">W-16-2020 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">화학물질의 유해…지침</t>
+    <t xml:space="preserve">Merck(Millipore)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">merck-8.22287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7722-84-1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공급자 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Merck</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">D4</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">암모니아수 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MSDS (Ammonium hydroxide solution, Sigma-Aldrich Korea)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">암모니아수</t>
     </r>
     <r>
       <rPr>
@@ -1149,63 +1389,88 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">130</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">청크로 큰 편</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">K7</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">X-27-2012 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">화학물질 리스크 관리를 위한 작업공정별 관리요령에 관한 지침</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">X-27-2012_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">화학물질 리스크…지침</t>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sigma-221228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1336-21-6</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">항목 줄이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개로 잡힘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">적재 시 확인</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">D5</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">염산 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MSDS (Hydrochloric acid, Sigma-Aldrich Korea)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">염산</t>
     </r>
     <r>
       <rPr>
@@ -1218,510 +1483,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">2012-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K8</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">H-123-2013 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">불산</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">불화수소 취급근로자의 중독 예방 및 응급대응 지침</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">H-123-2013 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">불산</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">불화수소…지침</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.pdf</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2013-12</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">불산 응급대응 근거</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, 26</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">청크</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">D1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSDS</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">황산 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MSDS (Sulfuric acid, Sigma-Aldrich Korea)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Sigma-Aldrich_MSDS.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sigma-Aldrich Korea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개 항목 전체</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">sigma-339741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7664-93-9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.sigmaaldrich.com/KR/ko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D2</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">불산 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MSDS (Hydrofluoric acid, Sigma-Aldrich Korea)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">불산</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">한국어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.pdf</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sigma-695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7664-39-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D3</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">과산화수소 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MSDS (Hydrogen peroxide 30%, Merck(Millipore))</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">과산화수소</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">한국어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.pdf</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Merck(Millipore)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">merck-8.22287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7722-84-1</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">공급자 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Merck</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">D4</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">암모니아수 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MSDS (Ammonium hydroxide solution, Sigma-Aldrich Korea)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">암모니아수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">한국어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.pdf</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sigma-221228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1336-21-6</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">항목 줄이 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개로 잡힘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">적재 시 확인</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">D5</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">염산 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MSDS (Hydrochloric acid, Sigma-Aldrich Korea)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">염산</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">한국어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.pdf</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">2026-06-09</t>
   </si>
   <si>
@@ -1760,23 +1521,6 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">질산</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">한국어</t>
     </r>
     <r>
       <rPr>
@@ -3269,7 +3013,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
         <v>44</v>
       </c>
@@ -3304,7 +3048,7 @@
       </c>
       <c r="M7" s="6"/>
     </row>
-    <row r="8" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
@@ -3567,7 +3311,7 @@
       <c r="C15" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>85</v>
       </c>
       <c r="E15" s="6" t="s">
